--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/81.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/81.xlsx
@@ -426,13 +426,13 @@
         <v>-10.65704213332008</v>
       </c>
       <c r="E2">
-        <v>-7.290804472790809</v>
+        <v>-6.353881314499843</v>
       </c>
       <c r="F2">
-        <v>-5.303006966691062</v>
+        <v>-5.630309838150398</v>
       </c>
       <c r="G2">
-        <v>-5.111682096035403</v>
+        <v>-6.231520472331431</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.83889961821468</v>
       </c>
       <c r="E3">
-        <v>-7.382804950730639</v>
+        <v>-7.042576170060358</v>
       </c>
       <c r="F3">
-        <v>-5.194948095730672</v>
+        <v>-5.551000286271567</v>
       </c>
       <c r="G3">
-        <v>-4.761108565608741</v>
+        <v>-6.115512335544291</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.0972617857163</v>
       </c>
       <c r="E4">
-        <v>-7.705458723777152</v>
+        <v>-7.327756820693399</v>
       </c>
       <c r="F4">
-        <v>-5.320338069492434</v>
+        <v>-5.600703987174343</v>
       </c>
       <c r="G4">
-        <v>-4.58873176992443</v>
+        <v>-6.27109473370788</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.36667358646836</v>
       </c>
       <c r="E5">
-        <v>-9.152840529160736</v>
+        <v>-8.699648964369118</v>
       </c>
       <c r="F5">
-        <v>-5.308737612383629</v>
+        <v>-5.613890767859509</v>
       </c>
       <c r="G5">
-        <v>-5.073706828154423</v>
+        <v>-5.931263923556153</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.6123988756269</v>
       </c>
       <c r="E6">
-        <v>-10.78442254328032</v>
+        <v>-9.49224965603563</v>
       </c>
       <c r="F6">
-        <v>-4.956842169469983</v>
+        <v>-5.260749460372051</v>
       </c>
       <c r="G6">
-        <v>-5.720918481081941</v>
+        <v>-5.688296365337962</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.78931231050407</v>
       </c>
       <c r="E7">
-        <v>-10.24860444174475</v>
+        <v>-9.98853417948424</v>
       </c>
       <c r="F7">
-        <v>-4.843380686308534</v>
+        <v>-5.390123052973875</v>
       </c>
       <c r="G7">
-        <v>-5.090640268587795</v>
+        <v>-6.334448643692912</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-11.87047347855361</v>
       </c>
       <c r="E8">
-        <v>-12.62459059866721</v>
+        <v>-10.32912523807513</v>
       </c>
       <c r="F8">
-        <v>-5.026844185210957</v>
+        <v>-5.475486313832365</v>
       </c>
       <c r="G8">
-        <v>-6.041862628932125</v>
+        <v>-6.138735812502278</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.83617425537405</v>
       </c>
       <c r="E9">
-        <v>-11.89580063424278</v>
+        <v>-11.24193880074926</v>
       </c>
       <c r="F9">
-        <v>-4.983843633331635</v>
+        <v>-5.144319108438969</v>
       </c>
       <c r="G9">
-        <v>-4.72518583596211</v>
+        <v>-6.000808553699623</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.68098443668267</v>
       </c>
       <c r="E10">
-        <v>-13.00393180934174</v>
+        <v>-11.90775127714902</v>
       </c>
       <c r="F10">
-        <v>-4.946117296705937</v>
+        <v>-5.084765290749504</v>
       </c>
       <c r="G10">
-        <v>-4.538457825365057</v>
+        <v>-5.991380120003779</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.41528464945462</v>
       </c>
       <c r="E11">
-        <v>-13.25294806654952</v>
+        <v>-12.49539323522837</v>
       </c>
       <c r="F11">
-        <v>-4.321212667014644</v>
+        <v>-4.837151363439482</v>
       </c>
       <c r="G11">
-        <v>-4.647563474702818</v>
+        <v>-5.859564128266618</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.06043005641415</v>
       </c>
       <c r="E12">
-        <v>-13.89841863770683</v>
+        <v>-13.53748114539947</v>
       </c>
       <c r="F12">
-        <v>-4.583271665094684</v>
+        <v>-4.70974017321489</v>
       </c>
       <c r="G12">
-        <v>-4.018867702976445</v>
+        <v>-5.936468101143888</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.64544702824423</v>
       </c>
       <c r="E13">
-        <v>-14.51581267001657</v>
+        <v>-14.99202699666319</v>
       </c>
       <c r="F13">
-        <v>-4.443958492026669</v>
+        <v>-4.483200740999489</v>
       </c>
       <c r="G13">
-        <v>-4.418824641212415</v>
+        <v>-5.957768151143558</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.20771939709575</v>
       </c>
       <c r="E14">
-        <v>-15.47416909578584</v>
+        <v>-15.22674686142876</v>
       </c>
       <c r="F14">
-        <v>-4.310942567954736</v>
+        <v>-4.475813360501324</v>
       </c>
       <c r="G14">
-        <v>-4.347336720837393</v>
+        <v>-5.330691236185888</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.775337186360998</v>
       </c>
       <c r="E15">
-        <v>-16.95507519424821</v>
+        <v>-16.48102094970325</v>
       </c>
       <c r="F15">
-        <v>-4.036808458244087</v>
+        <v>-4.234770043430307</v>
       </c>
       <c r="G15">
-        <v>-3.373476850095527</v>
+        <v>-4.971910863367373</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.374970921283648</v>
       </c>
       <c r="E16">
-        <v>-16.70414792100919</v>
+        <v>-16.82095085108903</v>
       </c>
       <c r="F16">
-        <v>-3.611164293826603</v>
+        <v>-3.771611604442242</v>
       </c>
       <c r="G16">
-        <v>-3.473799622117601</v>
+        <v>-4.798620357114223</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.030553940972375</v>
       </c>
       <c r="E17">
-        <v>-18.7179603122202</v>
+        <v>-18.14667520225655</v>
       </c>
       <c r="F17">
-        <v>-3.633677663099887</v>
+        <v>-3.637173373539702</v>
       </c>
       <c r="G17">
-        <v>-2.86989652593483</v>
+        <v>-4.144145367273545</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.758613479733352</v>
       </c>
       <c r="E18">
-        <v>-19.73404572463925</v>
+        <v>-18.91114048491341</v>
       </c>
       <c r="F18">
-        <v>-3.403569624113227</v>
+        <v>-3.276131926131745</v>
       </c>
       <c r="G18">
-        <v>-3.294364743343563</v>
+        <v>-4.326486905031063</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.575395988770476</v>
       </c>
       <c r="E19">
-        <v>-19.78716925322323</v>
+        <v>-19.76931800868499</v>
       </c>
       <c r="F19">
-        <v>-3.001755933139479</v>
+        <v>-2.924894206935921</v>
       </c>
       <c r="G19">
-        <v>-2.926566444476074</v>
+        <v>-3.991472938638976</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.49156134745281</v>
       </c>
       <c r="E20">
-        <v>-19.74043087299006</v>
+        <v>-20.47548824544111</v>
       </c>
       <c r="F20">
-        <v>-2.558784807757638</v>
+        <v>-2.408578603342809</v>
       </c>
       <c r="G20">
-        <v>-2.77214273725123</v>
+        <v>-4.797057779619688</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.511259795228103</v>
       </c>
       <c r="E21">
-        <v>-21.59850904307729</v>
+        <v>-21.3036782143339</v>
       </c>
       <c r="F21">
-        <v>-2.347965303745164</v>
+        <v>-2.485910013863754</v>
       </c>
       <c r="G21">
-        <v>-2.535475147194272</v>
+        <v>-4.099628461406965</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.63547493964775</v>
       </c>
       <c r="E22">
-        <v>-22.1605062528512</v>
+        <v>-21.39597304308423</v>
       </c>
       <c r="F22">
-        <v>-2.163161506385011</v>
+        <v>-2.205498535974691</v>
       </c>
       <c r="G22">
-        <v>-3.558000037363424</v>
+        <v>-4.200580237081501</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.849990624737547</v>
       </c>
       <c r="E23">
-        <v>-22.59655301504978</v>
+        <v>-22.43611370943203</v>
       </c>
       <c r="F23">
-        <v>-2.039768726431399</v>
+        <v>-1.741356824879502</v>
       </c>
       <c r="G23">
-        <v>-2.600845179412721</v>
+        <v>-4.642961816403231</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.132926643805407</v>
       </c>
       <c r="E24">
-        <v>-22.91966869244508</v>
+        <v>-22.88357675460394</v>
       </c>
       <c r="F24">
-        <v>-1.837887306695132</v>
+        <v>-1.528810174832191</v>
       </c>
       <c r="G24">
-        <v>-2.93339609992359</v>
+        <v>-3.72304397467825</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.455238236250674</v>
       </c>
       <c r="E25">
-        <v>-22.16061946470139</v>
+        <v>-23.65072289387334</v>
       </c>
       <c r="F25">
-        <v>-1.591426466809806</v>
+        <v>-1.613461868091676</v>
       </c>
       <c r="G25">
-        <v>-3.524285441591487</v>
+        <v>-4.087402616730437</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.775772314029652</v>
       </c>
       <c r="E26">
-        <v>-23.99202039440943</v>
+        <v>-23.6547758781102</v>
       </c>
       <c r="F26">
-        <v>-1.208007502382624</v>
+        <v>-1.314133792192283</v>
       </c>
       <c r="G26">
-        <v>-3.104759868672885</v>
+        <v>-4.222876761288492</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.05228693134954</v>
       </c>
       <c r="E27">
-        <v>-23.32360404545527</v>
+        <v>-23.27380894526692</v>
       </c>
       <c r="F27">
-        <v>-1.336732483308056</v>
+        <v>-1.365544758312228</v>
       </c>
       <c r="G27">
-        <v>-4.323232638765959</v>
+        <v>-4.322034221280743</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.24518734975371</v>
       </c>
       <c r="E28">
-        <v>-23.75766280756448</v>
+        <v>-23.03704221024988</v>
       </c>
       <c r="F28">
-        <v>-1.418416964530712</v>
+        <v>-1.396288786099729</v>
       </c>
       <c r="G28">
-        <v>-3.644901857769293</v>
+        <v>-4.622949568618337</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.31689027536715</v>
       </c>
       <c r="E29">
-        <v>-23.58479284079567</v>
+        <v>-22.97333110943597</v>
       </c>
       <c r="F29">
-        <v>-1.415718143532392</v>
+        <v>-1.566336874913814</v>
       </c>
       <c r="G29">
-        <v>-3.352686624108904</v>
+        <v>-4.669615018539903</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.24016236038655</v>
       </c>
       <c r="E30">
-        <v>-23.3486555636657</v>
+        <v>-22.65403293562914</v>
       </c>
       <c r="F30">
-        <v>-1.558915531352134</v>
+        <v>-1.350758400172257</v>
       </c>
       <c r="G30">
-        <v>-4.354335214107412</v>
+        <v>-4.608105082420245</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.00056332966951</v>
       </c>
       <c r="E31">
-        <v>-23.44503507597095</v>
+        <v>-22.3249306155957</v>
       </c>
       <c r="F31">
-        <v>-1.540629320935335</v>
+        <v>-1.761894537897111</v>
       </c>
       <c r="G31">
-        <v>-3.84800713714912</v>
+        <v>-4.291441469952338</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.593675758874365</v>
       </c>
       <c r="E32">
-        <v>-22.11611362215401</v>
+        <v>-22.69968448210047</v>
       </c>
       <c r="F32">
-        <v>-1.446578971123687</v>
+        <v>-1.756436425080065</v>
       </c>
       <c r="G32">
-        <v>-2.74547960347794</v>
+        <v>-5.140424252407356</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.033245070675024</v>
       </c>
       <c r="E33">
-        <v>-22.52507558131271</v>
+        <v>-22.84916488061966</v>
       </c>
       <c r="F33">
-        <v>-1.574498778933598</v>
+        <v>-1.765127655870237</v>
       </c>
       <c r="G33">
-        <v>-3.585533844613543</v>
+        <v>-4.881850782517041</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.342225678206335</v>
       </c>
       <c r="E34">
-        <v>-22.32369434219161</v>
+        <v>-21.7419212864262</v>
       </c>
       <c r="F34">
-        <v>-1.726983822073528</v>
+        <v>-1.853698355312366</v>
       </c>
       <c r="G34">
-        <v>-4.029282679242992</v>
+        <v>-4.35084920965456</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.547390452206488</v>
       </c>
       <c r="E35">
-        <v>-22.53832589625916</v>
+        <v>-21.29670436436209</v>
       </c>
       <c r="F35">
-        <v>-1.714559967766341</v>
+        <v>-1.794190097830055</v>
       </c>
       <c r="G35">
-        <v>-3.107610248382197</v>
+        <v>-4.619635712533526</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.687056872406762</v>
       </c>
       <c r="E36">
-        <v>-19.90537148177144</v>
+        <v>-21.04259357389568</v>
       </c>
       <c r="F36">
-        <v>-1.951042293917544</v>
+        <v>-1.925755550579686</v>
       </c>
       <c r="G36">
-        <v>-3.467946577604169</v>
+        <v>-4.090961453185153</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.795834464228441</v>
       </c>
       <c r="E37">
-        <v>-21.11171620114876</v>
+        <v>-20.54734154252081</v>
       </c>
       <c r="F37">
-        <v>-1.902740190660305</v>
+        <v>-1.753457615899598</v>
       </c>
       <c r="G37">
-        <v>-3.379826476439849</v>
+        <v>-3.918263534583533</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.905754267106576</v>
       </c>
       <c r="E38">
-        <v>-19.91408879423621</v>
+        <v>-20.57971107472764</v>
       </c>
       <c r="F38">
-        <v>-1.873097891518527</v>
+        <v>-2.018552580510898</v>
       </c>
       <c r="G38">
-        <v>-2.045494544108901</v>
+        <v>-3.786712386489514</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.051707191831901</v>
       </c>
       <c r="E39">
-        <v>-20.50900801004589</v>
+        <v>-20.02474205661363</v>
       </c>
       <c r="F39">
-        <v>-1.637279087656967</v>
+        <v>-2.137458922610948</v>
       </c>
       <c r="G39">
-        <v>-3.059604027517226</v>
+        <v>-3.339235877582845</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.257181402923575</v>
       </c>
       <c r="E40">
-        <v>-20.29424965870612</v>
+        <v>-19.40732991040785</v>
       </c>
       <c r="F40">
-        <v>-1.638942449401788</v>
+        <v>-2.493275856809448</v>
       </c>
       <c r="G40">
-        <v>-2.107252771144005</v>
+        <v>-3.560314108695375</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.544752598239446</v>
       </c>
       <c r="E41">
-        <v>-19.48837600972313</v>
+        <v>-18.75508021366107</v>
       </c>
       <c r="F41">
-        <v>-1.619204939295285</v>
+        <v>-2.18994593798713</v>
       </c>
       <c r="G41">
-        <v>-2.902498778405572</v>
+        <v>-3.024621492803747</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.932035711013257</v>
       </c>
       <c r="E42">
-        <v>-18.54325178500427</v>
+        <v>-18.03007152503304</v>
       </c>
       <c r="F42">
-        <v>-1.697280223743943</v>
+        <v>-2.226428895141226</v>
       </c>
       <c r="G42">
-        <v>-2.322481268288643</v>
+        <v>-3.279576536419639</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.42148221343057</v>
       </c>
       <c r="E43">
-        <v>-17.66859061584477</v>
+        <v>-18.07720388250488</v>
       </c>
       <c r="F43">
-        <v>-2.439806397693545</v>
+        <v>-2.324394937665907</v>
       </c>
       <c r="G43">
-        <v>-2.132992262711838</v>
+        <v>-2.773976779479986</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.017510674734666</v>
       </c>
       <c r="E44">
-        <v>-17.31089098245289</v>
+        <v>-16.48327612975907</v>
       </c>
       <c r="F44">
-        <v>-1.866993652127298</v>
+        <v>-2.360414837441837</v>
       </c>
       <c r="G44">
-        <v>-2.114310854233731</v>
+        <v>-2.666701861825443</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7132471414706479</v>
       </c>
       <c r="E45">
-        <v>-16.90987196670364</v>
+        <v>-16.88088520458055</v>
       </c>
       <c r="F45">
-        <v>-1.919309195451101</v>
+        <v>-2.213679492444739</v>
       </c>
       <c r="G45">
-        <v>-2.06734745521363</v>
+        <v>-2.847470890451806</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.4959745548585716</v>
       </c>
       <c r="E46">
-        <v>-17.03513408622981</v>
+        <v>-16.53745932126085</v>
       </c>
       <c r="F46">
-        <v>-2.083823790014485</v>
+        <v>-2.338217076149019</v>
       </c>
       <c r="G46">
-        <v>-2.323179793397429</v>
+        <v>-2.546320494380924</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.3568807159308786</v>
       </c>
       <c r="E47">
-        <v>-16.8566488116915</v>
+        <v>-15.52644579973039</v>
       </c>
       <c r="F47">
-        <v>-1.857453344749256</v>
+        <v>-2.375367697429771</v>
       </c>
       <c r="G47">
-        <v>-1.419053253894771</v>
+        <v>-2.078950917328775</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.2832740462358693</v>
       </c>
       <c r="E48">
-        <v>-15.35890584686861</v>
+        <v>-15.12802159958754</v>
       </c>
       <c r="F48">
-        <v>-2.266299874972772</v>
+        <v>-2.584779805224889</v>
       </c>
       <c r="G48">
-        <v>-1.911884236689455</v>
+        <v>-2.200514149530814</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2659226690407469</v>
       </c>
       <c r="E49">
-        <v>-14.26634809388203</v>
+        <v>-14.5978369197175</v>
       </c>
       <c r="F49">
-        <v>-1.966544361493534</v>
+        <v>-2.495200982653553</v>
       </c>
       <c r="G49">
-        <v>-1.829478137125917</v>
+        <v>-2.360118860524616</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.2975694178915355</v>
       </c>
       <c r="E50">
-        <v>-14.31345328050982</v>
+        <v>-13.80851484323255</v>
       </c>
       <c r="F50">
-        <v>-2.135263748993529</v>
+        <v>-2.928949065372625</v>
       </c>
       <c r="G50">
-        <v>-1.795958863540796</v>
+        <v>-2.085754088411978</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.3727118028650648</v>
       </c>
       <c r="E51">
-        <v>-14.04885907271564</v>
+        <v>-13.9632890278667</v>
       </c>
       <c r="F51">
-        <v>-1.912935736653961</v>
+        <v>-2.693904785032682</v>
       </c>
       <c r="G51">
-        <v>-2.917028762777433</v>
+        <v>-1.974807775754382</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.4918611770228394</v>
       </c>
       <c r="E52">
-        <v>-14.26394800265796</v>
+        <v>-12.80926176870001</v>
       </c>
       <c r="F52">
-        <v>-2.574202381858542</v>
+        <v>-2.777298188207314</v>
       </c>
       <c r="G52">
-        <v>-2.440200957119587</v>
+        <v>-2.112751587284734</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6553224614876432</v>
       </c>
       <c r="E53">
-        <v>-14.22225887094335</v>
+        <v>-12.77973611816999</v>
       </c>
       <c r="F53">
-        <v>-2.801866737006944</v>
+        <v>-2.688496374259804</v>
       </c>
       <c r="G53">
-        <v>-1.151789601963869</v>
+        <v>-2.305537896218652</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.8689708894780254</v>
       </c>
       <c r="E54">
-        <v>-12.83283247590993</v>
+        <v>-11.78800031049019</v>
       </c>
       <c r="F54">
-        <v>-2.252380817503532</v>
+        <v>-2.889501381283909</v>
       </c>
       <c r="G54">
-        <v>-1.706617171072484</v>
+        <v>-1.653661684626302</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.136822690841773</v>
       </c>
       <c r="E55">
-        <v>-12.31919031158992</v>
+        <v>-11.10460376951865</v>
       </c>
       <c r="F55">
-        <v>-2.515600358314894</v>
+        <v>-2.719064788157911</v>
       </c>
       <c r="G55">
-        <v>-1.916326988803157</v>
+        <v>-1.968170131948144</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.461291253631334</v>
       </c>
       <c r="E56">
-        <v>-11.69486318557443</v>
+        <v>-10.94843934336413</v>
       </c>
       <c r="F56">
-        <v>-2.368833535356489</v>
+        <v>-2.980436241293628</v>
       </c>
       <c r="G56">
-        <v>-1.46970791119116</v>
+        <v>-1.687144542210491</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.847317805022267</v>
       </c>
       <c r="E57">
-        <v>-11.90835356419204</v>
+        <v>-11.41905647613727</v>
       </c>
       <c r="F57">
-        <v>-2.756044765753687</v>
+        <v>-3.050403465603686</v>
       </c>
       <c r="G57">
-        <v>-2.507007766102079</v>
+        <v>-2.339725900002706</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.292268722028526</v>
       </c>
       <c r="E58">
-        <v>-11.10570418870251</v>
+        <v>-10.59713391527109</v>
       </c>
       <c r="F58">
-        <v>-2.312239474397227</v>
+        <v>-3.029961843204802</v>
       </c>
       <c r="G58">
-        <v>-2.788513384942926</v>
+        <v>-2.281897290522717</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.791901564540578</v>
       </c>
       <c r="E59">
-        <v>-11.39343889867588</v>
+        <v>-10.41861694141472</v>
       </c>
       <c r="F59">
-        <v>-2.747856353977014</v>
+        <v>-3.142616496515924</v>
       </c>
       <c r="G59">
-        <v>-2.386381418287655</v>
+        <v>-2.500121831380395</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.336813694460404</v>
       </c>
       <c r="E60">
-        <v>-9.663982975828512</v>
+        <v>-9.794366799457357</v>
       </c>
       <c r="F60">
-        <v>-2.541043663091881</v>
+        <v>-2.861896037585616</v>
       </c>
       <c r="G60">
-        <v>-2.40103058229893</v>
+        <v>-2.115231185893649</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.907977231936539</v>
       </c>
       <c r="E61">
-        <v>-10.55350659668119</v>
+        <v>-8.797654198843119</v>
       </c>
       <c r="F61">
-        <v>-3.172277019740563</v>
+        <v>-2.896183821122293</v>
       </c>
       <c r="G61">
-        <v>-2.606340685007911</v>
+        <v>-2.75002167195782</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.489326191575157</v>
       </c>
       <c r="E62">
-        <v>-9.487694011183914</v>
+        <v>-8.675747678556634</v>
       </c>
       <c r="F62">
-        <v>-2.323776975583418</v>
+        <v>-2.757559021366004</v>
       </c>
       <c r="G62">
-        <v>-2.196538184338149</v>
+        <v>-2.592658200294103</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.061521557797339</v>
       </c>
       <c r="E63">
-        <v>-10.1767873724571</v>
+        <v>-8.592586781879776</v>
       </c>
       <c r="F63">
-        <v>-2.505138906384939</v>
+        <v>-2.987789658728279</v>
       </c>
       <c r="G63">
-        <v>-3.354623293249377</v>
+        <v>-2.787665885284873</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.603594556781744</v>
       </c>
       <c r="E64">
-        <v>-9.611330408541329</v>
+        <v>-8.229416751886635</v>
       </c>
       <c r="F64">
-        <v>-2.599045120268499</v>
+        <v>-2.988080415686662</v>
       </c>
       <c r="G64">
-        <v>-2.056406102206338</v>
+        <v>-2.981961802984698</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.103705259972566</v>
       </c>
       <c r="E65">
-        <v>-8.810415438596735</v>
+        <v>-9.014912267835113</v>
       </c>
       <c r="F65">
-        <v>-2.788675814484765</v>
+        <v>-2.974312949452134</v>
       </c>
       <c r="G65">
-        <v>-2.897672003009315</v>
+        <v>-2.802785146762724</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.547443005351306</v>
       </c>
       <c r="E66">
-        <v>-10.28149927693647</v>
+        <v>-8.943670314746443</v>
       </c>
       <c r="F66">
-        <v>-3.034232905533636</v>
+        <v>-2.736380151978629</v>
       </c>
       <c r="G66">
-        <v>-2.929966374744905</v>
+        <v>-2.876858603203917</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.924757348071483</v>
       </c>
       <c r="E67">
-        <v>-8.970854744214488</v>
+        <v>-7.921317494300776</v>
       </c>
       <c r="F67">
-        <v>-2.661163563437031</v>
+        <v>-3.010765257012327</v>
       </c>
       <c r="G67">
-        <v>-3.145310740983418</v>
+        <v>-2.788460416214298</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.230542113112257</v>
       </c>
       <c r="E68">
-        <v>-9.078990175043648</v>
+        <v>-8.268556352734931</v>
       </c>
       <c r="F68">
-        <v>-2.666051759480951</v>
+        <v>-3.216049610039295</v>
       </c>
       <c r="G68">
-        <v>-2.607916504684604</v>
+        <v>-2.185216118593841</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.458426326544014</v>
       </c>
       <c r="E69">
-        <v>-9.469177080966549</v>
+        <v>-7.894164764150783</v>
       </c>
       <c r="F69">
-        <v>-2.883887535395137</v>
+        <v>-3.273942551086146</v>
       </c>
       <c r="G69">
-        <v>-2.825171055699276</v>
+        <v>-2.141738724026593</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.605192990991333</v>
       </c>
       <c r="E70">
-        <v>-8.226319275665389</v>
+        <v>-8.037930228472295</v>
       </c>
       <c r="F70">
-        <v>-2.833683500581071</v>
+        <v>-3.318765511251628</v>
       </c>
       <c r="G70">
-        <v>-3.184626779807802</v>
+        <v>-2.598064321159733</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.667826823463249</v>
       </c>
       <c r="E71">
-        <v>-9.212371848465571</v>
+        <v>-7.664009601184945</v>
       </c>
       <c r="F71">
-        <v>-2.870135808141263</v>
+        <v>-3.181580414041404</v>
       </c>
       <c r="G71">
-        <v>-2.39044676820988</v>
+        <v>-2.65554201281256</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.642078859623722</v>
       </c>
       <c r="E72">
-        <v>-9.785015500631518</v>
+        <v>-7.496976837412024</v>
       </c>
       <c r="F72">
-        <v>-2.923551423375983</v>
+        <v>-3.409956336788811</v>
       </c>
       <c r="G72">
-        <v>-2.798074240460341</v>
+        <v>-2.720713412298652</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.524563565412698</v>
       </c>
       <c r="E73">
-        <v>-9.74704877455121</v>
+        <v>-7.975247091258121</v>
       </c>
       <c r="F73">
-        <v>-2.901896242731999</v>
+        <v>-3.476489149846862</v>
       </c>
       <c r="G73">
-        <v>-3.17237114022142</v>
+        <v>-2.944552638390934</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.315636918400044</v>
       </c>
       <c r="E74">
-        <v>-10.35588399098646</v>
+        <v>-8.371388940501109</v>
       </c>
       <c r="F74">
-        <v>-2.957074623799877</v>
+        <v>-3.471281203985461</v>
       </c>
       <c r="G74">
-        <v>-2.000931290604771</v>
+        <v>-2.500985883766145</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.01806773586642</v>
       </c>
       <c r="E75">
-        <v>-10.25758440570196</v>
+        <v>-8.472645619312619</v>
       </c>
       <c r="F75">
-        <v>-2.999647738099354</v>
+        <v>-3.509784549234985</v>
       </c>
       <c r="G75">
-        <v>-1.626925718851148</v>
+        <v>-1.093656422294267</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.640371602722705</v>
       </c>
       <c r="E76">
-        <v>-9.286797318781634</v>
+        <v>-8.683699678914103</v>
       </c>
       <c r="F76">
-        <v>-3.390816079579726</v>
+        <v>-3.581131833638107</v>
       </c>
       <c r="G76">
-        <v>-2.073412374641575</v>
+        <v>-1.265318140142096</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.200571990224607</v>
       </c>
       <c r="E77">
-        <v>-9.674185627767795</v>
+        <v>-9.111174039816161</v>
       </c>
       <c r="F77">
-        <v>-3.277532695409879</v>
+        <v>-3.887107557944966</v>
       </c>
       <c r="G77">
-        <v>-0.6516522451640137</v>
+        <v>-1.402126434552478</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.720099438368431</v>
       </c>
       <c r="E78">
-        <v>-9.979087782704239</v>
+        <v>-9.117948636931636</v>
       </c>
       <c r="F78">
-        <v>-3.404209952115591</v>
+        <v>-3.738451228940775</v>
       </c>
       <c r="G78">
-        <v>-1.172096488301758</v>
+        <v>-1.175575871663533</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.226272892422201</v>
       </c>
       <c r="E79">
-        <v>-12.69887568628903</v>
+        <v>-10.04634467866616</v>
       </c>
       <c r="F79">
-        <v>-3.866531740026828</v>
+        <v>-3.77863284654837</v>
       </c>
       <c r="G79">
-        <v>-0.676329051613741</v>
+        <v>-0.3592483104078861</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.750143288263859</v>
       </c>
       <c r="E80">
-        <v>-11.1336856295959</v>
+        <v>-10.12388121062549</v>
       </c>
       <c r="F80">
-        <v>-3.560098756913624</v>
+        <v>-4.2165111691378</v>
       </c>
       <c r="G80">
-        <v>-1.779793469672535</v>
+        <v>-0.1636612799477443</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.319853201001264</v>
       </c>
       <c r="E81">
-        <v>-11.97674710712989</v>
+        <v>-10.93877105135776</v>
       </c>
       <c r="F81">
-        <v>-4.005719001249618</v>
+        <v>-4.035454905907912</v>
       </c>
       <c r="G81">
-        <v>-0.6867738227901417</v>
+        <v>-0.3510480891071113</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.963667383543531</v>
       </c>
       <c r="E82">
-        <v>-13.49842758555732</v>
+        <v>-11.91467984238076</v>
       </c>
       <c r="F82">
-        <v>-3.902646902054081</v>
+        <v>-4.557386840492005</v>
       </c>
       <c r="G82">
-        <v>-0.7513129080782335</v>
+        <v>0.112991079132531</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.701261838354367</v>
       </c>
       <c r="E83">
-        <v>-13.05383559290627</v>
+        <v>-12.88621865598636</v>
       </c>
       <c r="F83">
-        <v>-3.99306983100887</v>
+        <v>-4.702261672302416</v>
       </c>
       <c r="G83">
-        <v>-0.3139997739771275</v>
+        <v>0.322730691773057</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.545965248634793</v>
       </c>
       <c r="E84">
-        <v>-13.73515809278229</v>
+        <v>-13.59623809564899</v>
       </c>
       <c r="F84">
-        <v>-4.309965094419432</v>
+        <v>-4.715715187291283</v>
       </c>
       <c r="G84">
-        <v>-0.1101463113054256</v>
+        <v>0.4036172509340699</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.507488662750072</v>
       </c>
       <c r="E85">
-        <v>-15.33038098909429</v>
+        <v>-14.49521717022969</v>
       </c>
       <c r="F85">
-        <v>-4.495594774080176</v>
+        <v>-4.994927189181093</v>
       </c>
       <c r="G85">
-        <v>0.9113887257474846</v>
+        <v>0.790745825205364</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.583352294643077</v>
       </c>
       <c r="E86">
-        <v>-16.16546782390077</v>
+        <v>-15.31838958992198</v>
       </c>
       <c r="F86">
-        <v>-4.441999403119048</v>
+        <v>-5.238847426242033</v>
       </c>
       <c r="G86">
-        <v>0.5178509353121615</v>
+        <v>1.516516723779786</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.769181072054102</v>
       </c>
       <c r="E87">
-        <v>-17.51186918738731</v>
+        <v>-16.48236590648353</v>
       </c>
       <c r="F87">
-        <v>-4.614178881260536</v>
+        <v>-5.380766643159255</v>
       </c>
       <c r="G87">
-        <v>0.605739298288733</v>
+        <v>1.172994655351772</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.055256425240279</v>
       </c>
       <c r="E88">
-        <v>-18.27819114438731</v>
+        <v>-18.35278869671567</v>
       </c>
       <c r="F88">
-        <v>-4.94981678552684</v>
+        <v>-5.515739999404003</v>
       </c>
       <c r="G88">
-        <v>1.069083251965128</v>
+        <v>1.133847454349891</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.429099979082824</v>
       </c>
       <c r="E89">
-        <v>-19.91115434307924</v>
+        <v>-19.84656924678184</v>
       </c>
       <c r="F89">
-        <v>-5.356562576016856</v>
+        <v>-5.537577420876604</v>
       </c>
       <c r="G89">
-        <v>0.4009820566848101</v>
+        <v>1.540097739656015</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.879589145910477</v>
       </c>
       <c r="E90">
-        <v>-22.39174372110487</v>
+        <v>-20.17188576254486</v>
       </c>
       <c r="F90">
-        <v>-5.466015589316157</v>
+        <v>-5.706897374743629</v>
       </c>
       <c r="G90">
-        <v>0.2139097493516738</v>
+        <v>1.834133773363003</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.390073295474648</v>
       </c>
       <c r="E91">
-        <v>-24.47776715884219</v>
+        <v>-22.17927677761299</v>
       </c>
       <c r="F91">
-        <v>-5.178610205445258</v>
+        <v>-5.847965029970773</v>
       </c>
       <c r="G91">
-        <v>0.3925136811953544</v>
+        <v>1.040307990137783</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.946847273514039</v>
       </c>
       <c r="E92">
-        <v>-25.90299114090624</v>
+        <v>-25.12711410375006</v>
       </c>
       <c r="F92">
-        <v>-5.634188254330304</v>
+        <v>-6.193371042650889</v>
       </c>
       <c r="G92">
-        <v>0.2760917262158045</v>
+        <v>1.18127101919995</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.534180085389739</v>
       </c>
       <c r="E93">
-        <v>-27.55659512412513</v>
+        <v>-26.43179010772993</v>
       </c>
       <c r="F93">
-        <v>-5.531988426009915</v>
+        <v>-6.226807264497488</v>
       </c>
       <c r="G93">
-        <v>0.07588979527391877</v>
+        <v>0.9056482397823884</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.128812409765566</v>
       </c>
       <c r="E94">
-        <v>-30.06879777919832</v>
+        <v>-29.30362605459626</v>
       </c>
       <c r="F94">
-        <v>-5.793769921010019</v>
+        <v>-6.504040296662009</v>
       </c>
       <c r="G94">
-        <v>-0.6443988398874705</v>
+        <v>0.7303449218413612</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.714465461594081</v>
       </c>
       <c r="E95">
-        <v>-31.38089595207676</v>
+        <v>-31.50133977525876</v>
       </c>
       <c r="F95">
-        <v>-6.00920177472128</v>
+        <v>-6.688415828074915</v>
       </c>
       <c r="G95">
-        <v>-0.8187884472596588</v>
+        <v>0.08957890107880513</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.266626665789817</v>
       </c>
       <c r="E96">
-        <v>-33.91843768345986</v>
+        <v>-33.55245320687095</v>
       </c>
       <c r="F96">
-        <v>-5.9511820934618</v>
+        <v>-6.581377091571073</v>
       </c>
       <c r="G96">
-        <v>-1.278795371032469</v>
+        <v>-0.06369273629837229</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.763437123029799</v>
       </c>
       <c r="E97">
-        <v>-36.66822899158247</v>
+        <v>-35.93452789709673</v>
       </c>
       <c r="F97">
-        <v>-6.280330567494572</v>
+        <v>-7.071316234507945</v>
       </c>
       <c r="G97">
-        <v>-1.211323142396583</v>
+        <v>-0.1223688454364148</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.180604463714817</v>
       </c>
       <c r="E98">
-        <v>-39.23924293859327</v>
+        <v>-38.04712668454806</v>
       </c>
       <c r="F98">
-        <v>-6.219272434601623</v>
+        <v>-7.019747878581467</v>
       </c>
       <c r="G98">
-        <v>-2.93062848385276</v>
+        <v>-1.370348507921013</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.502098205199012</v>
       </c>
       <c r="E99">
-        <v>-41.82800850371414</v>
+        <v>-40.98356131313381</v>
       </c>
       <c r="F99">
-        <v>-6.704023098311061</v>
+        <v>-7.22642140374293</v>
       </c>
       <c r="G99">
-        <v>-2.40384454600731</v>
+        <v>-2.094934231192377</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.701757722682393</v>
       </c>
       <c r="E100">
-        <v>-44.25787897285387</v>
+        <v>-43.21070558637216</v>
       </c>
       <c r="F100">
-        <v>-6.487073261334169</v>
+        <v>-7.223351059964453</v>
       </c>
       <c r="G100">
-        <v>-3.66717520815751</v>
+        <v>-3.037112181123417</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.786663581683728</v>
       </c>
       <c r="E101">
-        <v>-46.4083788235124</v>
+        <v>-46.1882270596295</v>
       </c>
       <c r="F101">
-        <v>-6.683083212919393</v>
+        <v>-7.383066507979719</v>
       </c>
       <c r="G101">
-        <v>-4.499042470174495</v>
+        <v>-3.080043335676686</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.7218747490908</v>
       </c>
       <c r="E102">
-        <v>-49.38643692093965</v>
+        <v>-48.2102405172684</v>
       </c>
       <c r="F102">
-        <v>-6.881974640515256</v>
+        <v>-7.403769894477887</v>
       </c>
       <c r="G102">
-        <v>-4.856359581864652</v>
+        <v>-4.108811914732904</v>
       </c>
     </row>
   </sheetData>
